--- a/SeleniumTests/TestDataFolder/UserTestDataNegative.xlsx
+++ b/SeleniumTests/TestDataFolder/UserTestDataNegative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23567248-7127-487D-BA79-9790A3BAF298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B64FDA0-FE27-4923-8B86-ACA6B930F32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31155" yWindow="990" windowWidth="21600" windowHeight="11235" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MissingRolenameTestData" sheetId="2" r:id="rId1"/>
@@ -46,23 +46,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="64">
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>Rolename</t>
-  </si>
-  <si>
-    <t>RoleDesc</t>
-  </si>
-  <si>
-    <t>colorClass</t>
-  </si>
-  <si>
-    <t>EditStorePermission</t>
-  </si>
-  <si>
     <t>badge-info</t>
   </si>
   <si>
@@ -72,21 +60,6 @@
     <t>Username</t>
   </si>
   <si>
-    <t>CustEmail</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>UserPassword</t>
-  </si>
-  <si>
-    <t>UserConfirmPassword</t>
-  </si>
-  <si>
-    <t>activeUser</t>
-  </si>
-  <si>
     <t>Test1</t>
   </si>
   <si>
@@ -102,18 +75,9 @@
     <t>Manager without name</t>
   </si>
   <si>
-    <t>expectedMessage</t>
-  </si>
-  <si>
     <t>Role name is required</t>
   </si>
   <si>
-    <t>Rolename (No need Fill in)</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Test2</t>
   </si>
   <si>
@@ -126,9 +90,6 @@
     <t>missingatsign.com</t>
   </si>
   <si>
-    <t>expectedCase</t>
-  </si>
-  <si>
     <t>TestPwd1</t>
   </si>
   <si>
@@ -174,9 +135,6 @@
     <t>Empty Password</t>
   </si>
   <si>
-    <t>invalidFilePath</t>
-  </si>
-  <si>
     <t>D:\\e-invoice\\SeleniumTests\\InvalidFileType\\TestInvalidFileType.txt</t>
   </si>
   <si>
@@ -195,9 +153,6 @@
     <t>test_mandatory@qubeapps.com</t>
   </si>
   <si>
-    <t>expectedField</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
@@ -229,6 +184,60 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>User Role Desc</t>
+  </si>
+  <si>
+    <t>User Role Name (No need Fill in)</t>
+  </si>
+  <si>
+    <t>Color Class</t>
+  </si>
+  <si>
+    <t>Edit Store Permission</t>
+  </si>
+  <si>
+    <t>Expected Message</t>
+  </si>
+  <si>
+    <t>User Role Name</t>
+  </si>
+  <si>
+    <t>Role Name</t>
+  </si>
+  <si>
+    <t>Role Description</t>
+  </si>
+  <si>
+    <t>User Email</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>User Password</t>
+  </si>
+  <si>
+    <t>User Confirm Password</t>
+  </si>
+  <si>
+    <t>Active User</t>
+  </si>
+  <si>
+    <t>User Role</t>
+  </si>
+  <si>
+    <t>Expected Case</t>
+  </si>
+  <si>
+    <t>Invalid File Path</t>
+  </si>
+  <si>
+    <t>Active User (true/false)</t>
+  </si>
+  <si>
+    <t>Expected Field</t>
   </si>
 </sst>
 </file>
@@ -564,39 +573,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A206DD7-BE30-495A-A58C-776C5E69AA00}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -608,42 +624,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBA59B6-11EA-4CAA-A17F-088BA343A3CD}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
@@ -661,42 +685,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1798CB1-15D5-4E04-955E-780C87AF4AB7}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
@@ -714,36 +746,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1675D7BC-7B3D-4D47-9F79-C94ED20B8634}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
@@ -761,39 +800,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
@@ -801,19 +840,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>0</v>
@@ -831,112 +870,112 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1"/>
       <c r="F5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -955,51 +994,56 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="60.109375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>0</v>
@@ -1007,22 +1051,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>0</v>
@@ -1030,22 +1074,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>0</v>
@@ -1053,22 +1097,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>0</v>
@@ -1088,50 +1132,56 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1146,49 +1196,58 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39077C1B-ED1D-44BA-B649-06EBE5DA68D0}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1200,48 +1259,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C71182B1-4BB3-4211-AD5B-578CECE4A5D7}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1256,48 +1324,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7949B4-2715-4F62-8B79-0F3449CC3D28}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
